--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1227,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98549776</v>
+        <v>137138346</v>
       </c>
       <c r="B7" t="n">
-        <v>58114</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,21 +1238,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1261,22 +1261,27 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Utsträngsbo, Vstm</t>
+          <t>Usträngsbo Nyckelbiotop, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558961</v>
+        <v>558892</v>
       </c>
       <c r="R7" t="n">
-        <v>6625943</v>
+        <v>6626069</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1303,22 +1308,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2023-03-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2023-03-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,59 +1338,63 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98549776</t>
+          <t>https://artportalen.se/Sighting/137138346</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98550091</v>
+        <v>98549776</v>
       </c>
       <c r="B8" t="n">
-        <v>58636</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Utsträngsbo, Vstm</t>
@@ -1427,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,33 +1472,33 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98550091</t>
+          <t>https://artportalen.se/Sighting/98549776</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110818359</v>
+        <v>98550091</v>
       </c>
       <c r="B9" t="n">
-        <v>43258</v>
+        <v>58636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>201129</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1499,32 +1508,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Usträngsbo, Vstm</t>
+          <t>Utsträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558895</v>
+        <v>558961</v>
       </c>
       <c r="R9" t="n">
-        <v>6625916</v>
+        <v>6625943</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1551,22 +1550,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,79 +1574,74 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Blomrika vägkanter</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110818359</t>
+          <t>https://artportalen.se/Sighting/98550091</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110818386</v>
+        <v>110818359</v>
       </c>
       <c r="B10" t="n">
-        <v>99156</v>
+        <v>43258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219875</v>
+        <v>201129</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1688,9 +1682,19 @@
           <t>2023-07-13</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,6 +1725,130 @@
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110818359</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110818386</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>558895</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6625916</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Blomrika vägkanter</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110818386</t>
         </is>
@@ -1737,6 +1865,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>137138346</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>57862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>137138346</v>
       </c>
       <c r="B7" t="n">
-        <v>57862</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -1261,16 +1261,8 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -1230,7 +1230,7 @@
         <v>137138346</v>
       </c>
       <c r="B7" t="n">
-        <v>57864</v>
+        <v>57874</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,50 +992,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56832278</v>
+        <v>137362686</v>
       </c>
       <c r="B5" t="n">
-        <v>75428</v>
+        <v>92125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappkärrsmossen, S, Vstm</t>
+          <t>Usträngsbo N, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558907</v>
+        <v>558948</v>
       </c>
       <c r="R5" t="n">
-        <v>6625998</v>
+        <v>6625976</v>
       </c>
       <c r="S5" t="n">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,12 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-02-04</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-02-04</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,33 +1074,44 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56832278</t>
+          <t>https://artportalen.se/Sighting/137362686</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68881774</v>
+        <v>56832278</v>
       </c>
       <c r="B6" t="n">
-        <v>57874</v>
+        <v>75428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,56 +1119,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Usträngsbo Nyckelbiotop, Ramnäs sn, Vstm</t>
+          <t>Lappkärrsmossen, S, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558892</v>
+        <v>558907</v>
       </c>
       <c r="R6" t="n">
-        <v>6626069</v>
+        <v>6625998</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,22 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-01-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2016-02-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-01-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2016-02-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,24 +1195,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68881774</t>
+          <t>https://artportalen.se/Sighting/56832278</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137138346</v>
+        <v>68881774</v>
       </c>
       <c r="B7" t="n">
         <v>57874</v>
@@ -1238,16 +1223,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1260,10 +1245,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Usträngsbo Nyckelbiotop, Ramnäs sn, Vstm</t>
@@ -1300,22 +1296,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-03-19</t>
+          <t>2018-01-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-03-19</t>
+          <t>2018-01-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,16 +1337,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137138346</t>
+          <t>https://artportalen.se/Sighting/68881774</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98549776</v>
+        <v>137138346</v>
       </c>
       <c r="B8" t="n">
-        <v>58114</v>
+        <v>57875</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1354,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1382,21 +1378,18 @@
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Utsträngsbo, Vstm</t>
+          <t>Usträngsbo Nyckelbiotop, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558961</v>
+        <v>558892</v>
       </c>
       <c r="R8" t="n">
-        <v>6625943</v>
+        <v>6626069</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1423,22 +1416,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2023-03-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2023-03-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,59 +1446,63 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98549776</t>
+          <t>https://artportalen.se/Sighting/137138346</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98550091</v>
+        <v>98549776</v>
       </c>
       <c r="B9" t="n">
-        <v>58636</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Utsträngsbo, Vstm</t>
@@ -1547,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,33 +1580,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98550091</t>
+          <t>https://artportalen.se/Sighting/98549776</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110818359</v>
+        <v>98550091</v>
       </c>
       <c r="B10" t="n">
-        <v>43258</v>
+        <v>58636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>201129</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1619,32 +1616,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Usträngsbo, Vstm</t>
+          <t>Utsträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558895</v>
+        <v>558961</v>
       </c>
       <c r="R10" t="n">
-        <v>6625916</v>
+        <v>6625943</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1671,22 +1658,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-13</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,79 +1682,74 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Blomrika vägkanter</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110818359</t>
+          <t>https://artportalen.se/Sighting/98550091</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110818386</v>
+        <v>110818359</v>
       </c>
       <c r="B11" t="n">
-        <v>99156</v>
+        <v>43258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219875</v>
+        <v>201129</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1808,9 +1790,19 @@
           <t>2023-07-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,6 +1833,130 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110818359</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110818386</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99156</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>558895</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6625916</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-07-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Blomrika vägkanter</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110818386</t>
         </is>
@@ -1858,6 +1974,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -995,7 +995,7 @@
         <v>137362686</v>
       </c>
       <c r="B5" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -995,7 +995,7 @@
         <v>137362686</v>
       </c>
       <c r="B5" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137138346</v>
       </c>
       <c r="B8" t="n">
-        <v>57875</v>
+        <v>57876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -995,7 +995,7 @@
         <v>137362686</v>
       </c>
       <c r="B5" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -995,7 +995,7 @@
         <v>137362686</v>
       </c>
       <c r="B5" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -995,7 +995,7 @@
         <v>137362686</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20391-2024 artfynd.xlsx
+++ b/artfynd/A 20391-2024 artfynd.xlsx
@@ -995,7 +995,7 @@
         <v>137362686</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137138346</v>
       </c>
       <c r="B8" t="n">
-        <v>57876</v>
+        <v>57879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
